--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_individual_h_6.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755087492_individual_h_6.xlsx
@@ -658,7 +658,7 @@
         <v>0.008454177761639635</v>
       </c>
       <c r="C2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>27483344</v>
+        <v>4247596</v>
       </c>
       <c r="L2" t="n">
-        <v>15967046</v>
+        <v>2174098</v>
       </c>
       <c r="M2" t="n">
-        <v>3962351</v>
+        <v>490524</v>
       </c>
       <c r="N2" t="n">
-        <v>177895</v>
+        <v>12466</v>
       </c>
       <c r="O2" t="n">
-        <v>2351071</v>
+        <v>291221</v>
       </c>
       <c r="P2" t="n">
-        <v>930898</v>
+        <v>113653</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999120235443115</v>
+        <v>0.9998606443405151</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9020295739173889</v>
+        <v>0.8208213448524475</v>
       </c>
       <c r="S2" t="n">
-        <v>0.8026200532913208</v>
+        <v>0.6645370125770569</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7532739043235779</v>
+        <v>0.5693770051002502</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3957901298999786</v>
+        <v>0.1281126290559769</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7985839247703552</v>
+        <v>0.6322973966598511</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8613739013671875</v>
+        <v>0.7579848170280457</v>
       </c>
       <c r="X2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>37877868</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>28872412</v>
+        <v>4796855</v>
       </c>
       <c r="AG2" t="n">
-        <v>17836630</v>
+        <v>2983951</v>
       </c>
       <c r="AH2" t="n">
-        <v>4798928</v>
+        <v>801380</v>
       </c>
       <c r="AI2" t="n">
-        <v>353991</v>
+        <v>59049</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2755108</v>
+        <v>459641</v>
       </c>
       <c r="AK2" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9564692974090576</v>
+        <v>0.9560109972953796</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9113166332244873</v>
+        <v>0.9115679264068604</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581637144088745</v>
+        <v>0.8585426211357117</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6622001528739929</v>
+        <v>0.6615541577339172</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020119309425354</v>
+        <v>0.9020492434501648</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314349889755249</v>
+        <v>0.9314607977867126</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002027047184025982</v>
       </c>
       <c r="C3" t="n">
-        <v>1900</v>
+        <v>555</v>
       </c>
       <c r="D3" t="n">
-        <v>27483344</v>
+        <v>4247596</v>
       </c>
       <c r="E3" t="n">
-        <v>2617627</v>
+        <v>742217</v>
       </c>
       <c r="F3" t="n">
-        <v>42541</v>
+        <v>16909</v>
       </c>
       <c r="G3" t="n">
-        <v>4294</v>
+        <v>1350</v>
       </c>
       <c r="H3" t="n">
-        <v>2345</v>
+        <v>956</v>
       </c>
       <c r="I3" t="n">
-        <v>97</v>
+        <v>25</v>
       </c>
       <c r="J3" t="n">
-        <v>60096400</v>
+        <v>10015742</v>
       </c>
       <c r="K3" t="n">
-        <v>64840455</v>
+        <v>10392776</v>
       </c>
       <c r="L3" t="n">
-        <v>74450557</v>
+        <v>11952842</v>
       </c>
       <c r="M3" t="n">
-        <v>91083449</v>
+        <v>15023581</v>
       </c>
       <c r="N3" t="n">
-        <v>97171036</v>
+        <v>16155417</v>
       </c>
       <c r="O3" t="n">
-        <v>94328816</v>
+        <v>15650306</v>
       </c>
       <c r="P3" t="n">
-        <v>96667760</v>
+        <v>16099872</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9114887714385986</v>
+        <v>0.8478899002075195</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8146271705627441</v>
+        <v>0.6629847288131714</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7080268263816833</v>
+        <v>0.5246061086654663</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3325196206569672</v>
+        <v>0.1395281106233597</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7693786025047302</v>
+        <v>0.5710898637771606</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8024809956550598</v>
+        <v>0.5875362157821655</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>28872412</v>
+        <v>4796855</v>
       </c>
       <c r="Z3" t="n">
-        <v>1187392</v>
+        <v>197460</v>
       </c>
       <c r="AA3" t="n">
-        <v>51135</v>
+        <v>8429</v>
       </c>
       <c r="AB3" t="n">
-        <v>40793</v>
+        <v>6823</v>
       </c>
       <c r="AC3" t="n">
-        <v>236</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>60099732</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>66511414</v>
+        <v>11099274</v>
       </c>
       <c r="AG3" t="n">
-        <v>76641422</v>
+        <v>12760866</v>
       </c>
       <c r="AH3" t="n">
-        <v>91588110</v>
+        <v>15262528</v>
       </c>
       <c r="AI3" t="n">
-        <v>97262032</v>
+        <v>16210047</v>
       </c>
       <c r="AJ3" t="n">
-        <v>94622500</v>
+        <v>15769750</v>
       </c>
       <c r="AK3" t="n">
-        <v>96738050</v>
+        <v>16122905</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575573801994324</v>
+        <v>0.9575310349464417</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9100120067596436</v>
+        <v>0.9099469780921936</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8575135469436646</v>
+        <v>0.8570606708526611</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6616765260696411</v>
+        <v>0.660917341709137</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9015980958938599</v>
+        <v>0.9013646841049194</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9312928318977356</v>
+        <v>0.9312344789505005</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03199143872576704</v>
       </c>
       <c r="C4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2808436</v>
+        <v>871223</v>
       </c>
       <c r="E4" t="n">
-        <v>15967046</v>
+        <v>2174098</v>
       </c>
       <c r="F4" t="n">
-        <v>743839</v>
+        <v>203830</v>
       </c>
       <c r="G4" t="n">
-        <v>25850</v>
+        <v>9292</v>
       </c>
       <c r="H4" t="n">
-        <v>51300</v>
+        <v>19239</v>
       </c>
       <c r="I4" t="n">
-        <v>3958</v>
+        <v>1572</v>
       </c>
       <c r="J4" t="n">
-        <v>3332</v>
+        <v>880</v>
       </c>
       <c r="K4" t="n">
-        <v>2984997</v>
+        <v>927216</v>
       </c>
       <c r="L4" t="n">
-        <v>3926609</v>
+        <v>1097500</v>
       </c>
       <c r="M4" t="n">
-        <v>1297822</v>
+        <v>370986</v>
       </c>
       <c r="N4" t="n">
-        <v>271573</v>
+        <v>84839</v>
       </c>
       <c r="O4" t="n">
-        <v>592979</v>
+        <v>169355</v>
       </c>
       <c r="P4" t="n">
-        <v>149815</v>
+        <v>36288</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999560117721558</v>
+        <v>0.9999303221702576</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9067345261573792</v>
+        <v>0.8341361284255981</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8085790872573853</v>
+        <v>0.6637599468231201</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7299498319625854</v>
+        <v>0.5460754036903381</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3614066243171692</v>
+        <v>0.1335769295692444</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7837092876434326</v>
+        <v>0.6001370549201965</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8308852314949036</v>
+        <v>0.661964476108551</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1226769</v>
+        <v>206052</v>
       </c>
       <c r="Z4" t="n">
-        <v>17836630</v>
+        <v>2983951</v>
       </c>
       <c r="AA4" t="n">
-        <v>496804</v>
+        <v>82537</v>
       </c>
       <c r="AB4" t="n">
-        <v>32965</v>
+        <v>5520</v>
       </c>
       <c r="AC4" t="n">
-        <v>6858</v>
+        <v>1130</v>
       </c>
       <c r="AD4" t="n">
-        <v>408</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1314038</v>
+        <v>220718</v>
       </c>
       <c r="AG4" t="n">
-        <v>1735744</v>
+        <v>289476</v>
       </c>
       <c r="AH4" t="n">
-        <v>793161</v>
+        <v>132039</v>
       </c>
       <c r="AI4" t="n">
-        <v>180577</v>
+        <v>30209</v>
       </c>
       <c r="AJ4" t="n">
-        <v>299295</v>
+        <v>49911</v>
       </c>
       <c r="AK4" t="n">
-        <v>79525</v>
+        <v>13255</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9570130109786987</v>
+        <v>0.9567704200744629</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910663902759552</v>
+        <v>0.9107567667961121</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.85783851146698</v>
+        <v>0.8578009605407715</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6619382500648499</v>
+        <v>0.6612355709075928</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018049240112305</v>
+        <v>0.9017068147659302</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313638806343079</v>
+        <v>0.9313476085662842</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>1034</v>
+        <v>177</v>
       </c>
       <c r="D5" t="n">
-        <v>113092</v>
+        <v>38108</v>
       </c>
       <c r="E5" t="n">
-        <v>1120560</v>
+        <v>299599</v>
       </c>
       <c r="F5" t="n">
-        <v>3962351</v>
+        <v>490524</v>
       </c>
       <c r="G5" t="n">
-        <v>98755</v>
+        <v>27745</v>
       </c>
       <c r="H5" t="n">
-        <v>278989</v>
+        <v>71469</v>
       </c>
       <c r="I5" t="n">
-        <v>21548</v>
+        <v>7411</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>2668804</v>
+        <v>762012</v>
       </c>
       <c r="L5" t="n">
-        <v>3633388</v>
+        <v>1105160</v>
       </c>
       <c r="M5" t="n">
-        <v>1633978</v>
+        <v>444509</v>
       </c>
       <c r="N5" t="n">
-        <v>357096</v>
+        <v>76878</v>
       </c>
       <c r="O5" t="n">
-        <v>704734</v>
+        <v>218718</v>
       </c>
       <c r="P5" t="n">
-        <v>229127</v>
+        <v>79787</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999659657478333</v>
+        <v>0.999946117401123</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9422949552536011</v>
+        <v>0.8965542316436768</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9228395223617554</v>
+        <v>0.8651124238967896</v>
       </c>
       <c r="T5" t="n">
-        <v>0.970076858997345</v>
+        <v>0.9500603079795837</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9935835599899292</v>
+        <v>0.9900966882705688</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9867550134658813</v>
+        <v>0.9762349724769592</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9961323738098145</v>
+        <v>0.9928917288780212</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>48155</v>
+        <v>8093</v>
       </c>
       <c r="Z5" t="n">
-        <v>510890</v>
+        <v>85757</v>
       </c>
       <c r="AA5" t="n">
-        <v>4798928</v>
+        <v>801380</v>
       </c>
       <c r="AB5" t="n">
-        <v>59714</v>
+        <v>9985</v>
       </c>
       <c r="AC5" t="n">
-        <v>174844</v>
+        <v>29185</v>
       </c>
       <c r="AD5" t="n">
-        <v>3798</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1279736</v>
+        <v>212753</v>
       </c>
       <c r="AG5" t="n">
-        <v>1763804</v>
+        <v>295307</v>
       </c>
       <c r="AH5" t="n">
-        <v>797401</v>
+        <v>133653</v>
       </c>
       <c r="AI5" t="n">
-        <v>181000</v>
+        <v>30295</v>
       </c>
       <c r="AJ5" t="n">
-        <v>300697</v>
+        <v>50298</v>
       </c>
       <c r="AK5" t="n">
-        <v>79702</v>
+        <v>13302</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.9735268950462341</v>
+        <v>0.9734548926353455</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9642821550369263</v>
+        <v>0.9641887545585632</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837660789489746</v>
+        <v>0.9837294220924377</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963095784187317</v>
+        <v>0.9962948560714722</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938762187957764</v>
+        <v>0.9938633441925049</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.998374879360199</v>
+        <v>0.9983736872673035</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>211</v>
+        <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>61345</v>
+        <v>16455</v>
       </c>
       <c r="E6" t="n">
-        <v>108887</v>
+        <v>20162</v>
       </c>
       <c r="F6" t="n">
-        <v>121714</v>
+        <v>28164</v>
       </c>
       <c r="G6" t="n">
-        <v>177895</v>
+        <v>12466</v>
       </c>
       <c r="H6" t="n">
-        <v>60372</v>
+        <v>10979</v>
       </c>
       <c r="I6" t="n">
-        <v>4567</v>
+        <v>1077</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>38779</v>
+        <v>6517</v>
       </c>
       <c r="Z6" t="n">
-        <v>32116</v>
+        <v>5368</v>
       </c>
       <c r="AA6" t="n">
-        <v>65335</v>
+        <v>10940</v>
       </c>
       <c r="AB6" t="n">
-        <v>353991</v>
+        <v>59049</v>
       </c>
       <c r="AC6" t="n">
-        <v>41884</v>
+        <v>6989</v>
       </c>
       <c r="AD6" t="n">
-        <v>2886</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D7" t="n">
-        <v>1918</v>
+        <v>1368</v>
       </c>
       <c r="E7" t="n">
-        <v>75188</v>
+        <v>33270</v>
       </c>
       <c r="F7" t="n">
-        <v>373967</v>
+        <v>115156</v>
       </c>
       <c r="G7" t="n">
-        <v>133962</v>
+        <v>42686</v>
       </c>
       <c r="H7" t="n">
-        <v>2351071</v>
+        <v>291221</v>
       </c>
       <c r="I7" t="n">
-        <v>119645</v>
+        <v>26203</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>167</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>4860</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>177905</v>
+        <v>29802</v>
       </c>
       <c r="AB7" t="n">
-        <v>45512</v>
+        <v>7615</v>
       </c>
       <c r="AC7" t="n">
-        <v>2755108</v>
+        <v>459641</v>
       </c>
       <c r="AD7" t="n">
-        <v>72253</v>
+        <v>12043</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="D8" t="n">
-        <v>206</v>
+        <v>62</v>
       </c>
       <c r="E8" t="n">
-        <v>4347</v>
+        <v>2252</v>
       </c>
       <c r="F8" t="n">
-        <v>15761</v>
+        <v>6927</v>
       </c>
       <c r="G8" t="n">
-        <v>8712</v>
+        <v>3766</v>
       </c>
       <c r="H8" t="n">
-        <v>199973</v>
+        <v>66712</v>
       </c>
       <c r="I8" t="n">
-        <v>930898</v>
+        <v>113653</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>168</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>486</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>1982</v>
+        <v>331</v>
       </c>
       <c r="AB8" t="n">
-        <v>1593</v>
+        <v>266</v>
       </c>
       <c r="AC8" t="n">
-        <v>75473</v>
+        <v>12596</v>
       </c>
       <c r="AD8" t="n">
-        <v>1080323</v>
+        <v>180138</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
